--- a/Excel Projects/Budget Tracking System/Budget Tracking System.xlsx
+++ b/Excel Projects/Budget Tracking System/Budget Tracking System.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\razul\Downloads\Click consulting\For GIthub Uploads\Excel Projects\Budget Tracking System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\razul\Documents\Github\Portfolio\Excel Projects\Budget Tracking System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB1430C-7138-49E7-AD30-6D4106FA2B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE86958A-15A3-4D57-9C5F-F7880D00454F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{EF676F43-5E52-415C-A265-69AB6EB28E12}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="23640" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{EF676F43-5E52-415C-A265-69AB6EB28E12}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Data" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,16 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'Example Data'!$A$4:$A$9</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'Example Data'!$B$4:$B$9</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Summary!$A$4:$A$9</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Summary!$B$4:$B$9</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Summary!$A$4:$A$9</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Summary!$B$4:$B$9</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">'Example Data'!$A$4:$A$9</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">'Example Data'!$B$4:$B$9</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">Summary!$A$4:$A$9</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">Summary!$B$4:$B$9</definedName>
     <definedName name="_xlchart.v2.10" hidden="1">Summary!$A$12:$A$17</definedName>
     <definedName name="_xlchart.v2.11" hidden="1">Summary!$B$12:$B$17</definedName>
-    <definedName name="_xlchart.v2.14" hidden="1">Summary!$A$12:$A$17</definedName>
-    <definedName name="_xlchart.v2.15" hidden="1">Summary!$B$12:$B$17</definedName>
+    <definedName name="_xlchart.v2.12" hidden="1">Summary!$A$12:$A$17</definedName>
+    <definedName name="_xlchart.v2.13" hidden="1">Summary!$B$12:$B$17</definedName>
     <definedName name="_xlchart.v2.2" hidden="1">'Example Data'!$A$12:$A$17</definedName>
     <definedName name="_xlchart.v2.3" hidden="1">'Example Data'!$B$12:$B$17</definedName>
     <definedName name="_xlchart.v2.4" hidden="1">'Example Data'!$A$12:$A$17</definedName>
@@ -5632,10 +5632,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.12</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.15</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -5711,10 +5711,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.14</cx:f>
+        <cx:f>_xlchart.v2.12</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.15</cx:f>
+        <cx:f>_xlchart.v2.13</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -5776,7 +5776,7 @@
         <cx:series layoutId="funnel" uniqueId="{C6CAB302-544E-49E8-A2B7-D31BFBE5EBCA}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v2.15</cx:f>
+              <cx:f>_xlchart.v2.13</cx:f>
               <cx:v> $661.00   $250.00   $216.00   $100.00   $55.00   $40.00 </cx:v>
             </cx:txData>
           </cx:tx>
@@ -19838,13 +19838,13 @@
       <c r="H12" s="4">
         <v>45992</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="e">
         <f ca="1">IF(ISNUMBER(Goal_todo[[#This Row],[DeadLine]]),DATEDIF(TODAY(), Goal_todo[[#This Row],[DeadLine]], "m"),)</f>
-        <v>3</v>
-      </c>
-      <c r="J12" s="10">
+        <v>#NUM!</v>
+      </c>
+      <c r="J12" s="10" t="e">
         <f ca="1">IF(Goal_todo[[#This Row],[Current Savings]]&lt;Goal_todo[[#This Row],[Target Amount]], ROUND((Goal_todo[[#This Row],[Target Amount]]-Goal_todo[[#This Row],[Current Savings]])/DATEDIF(TODAY(),Goal_todo[[#This Row],[DeadLine]],"m"), 2), 0)</f>
-        <v>2886.86</v>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -19874,11 +19874,11 @@
       </c>
       <c r="I13">
         <f ca="1">IF(ISNUMBER(Goal_todo[[#This Row],[DeadLine]]),DATEDIF(TODAY(), Goal_todo[[#This Row],[DeadLine]], "m"),)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J13" s="10">
         <f ca="1">IF(Goal_todo[[#This Row],[Current Savings]]&lt;Goal_todo[[#This Row],[Target Amount]], ROUND((Goal_todo[[#This Row],[Target Amount]]-Goal_todo[[#This Row],[Current Savings]])/DATEDIF(TODAY(),Goal_todo[[#This Row],[DeadLine]],"m"), 2), 0)</f>
-        <v>444.04</v>
+        <v>666.06</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -19908,11 +19908,11 @@
       </c>
       <c r="I14">
         <f ca="1">IF(ISNUMBER(Goal_todo[[#This Row],[DeadLine]]),DATEDIF(TODAY(), Goal_todo[[#This Row],[DeadLine]], "m"),)</f>
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J14" s="10">
         <f ca="1">IF(Goal_todo[[#This Row],[Current Savings]]&lt;Goal_todo[[#This Row],[Target Amount]], ROUND((Goal_todo[[#This Row],[Target Amount]]-Goal_todo[[#This Row],[Current Savings]])/DATEDIF(TODAY(),Goal_todo[[#This Row],[DeadLine]],"m"), 2), 0)</f>
-        <v>29.76</v>
+        <v>31.02</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -19942,11 +19942,11 @@
       </c>
       <c r="I15">
         <f ca="1">IF(ISNUMBER(Goal_todo[[#This Row],[DeadLine]]),DATEDIF(TODAY(), Goal_todo[[#This Row],[DeadLine]], "m"),)</f>
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J15" s="10">
         <f ca="1">IF(Goal_todo[[#This Row],[Current Savings]]&lt;Goal_todo[[#This Row],[Target Amount]], ROUND((Goal_todo[[#This Row],[Target Amount]]-Goal_todo[[#This Row],[Current Savings]])/DATEDIF(TODAY(),Goal_todo[[#This Row],[DeadLine]],"m"), 2), 0)</f>
-        <v>414.54</v>
+        <v>423.44</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -19976,11 +19976,11 @@
       </c>
       <c r="I16">
         <f ca="1">IF(ISNUMBER(Goal_todo[[#This Row],[DeadLine]]),DATEDIF(TODAY(), Goal_todo[[#This Row],[DeadLine]], "m"),)</f>
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="J16" s="10">
         <f ca="1">IF(Goal_todo[[#This Row],[Current Savings]]&lt;Goal_todo[[#This Row],[Target Amount]], ROUND((Goal_todo[[#This Row],[Target Amount]]-Goal_todo[[#This Row],[Current Savings]])/DATEDIF(TODAY(),Goal_todo[[#This Row],[DeadLine]],"m"), 2), 0)</f>
-        <v>298.87</v>
+        <v>300.68</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
